--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>64923333</v>
+        <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>101326</v>
+        <v>106562</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6036,37 +6036,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Klämmeshöjden söder om, Vrm</t>
+          <t>Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446590</v>
+        <v>446666</v>
       </c>
       <c r="R50" t="n">
-        <v>6585573</v>
+        <v>6585810</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6090,17 +6090,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Kristinehams Naturskyddsförening utflykt 9/4-17</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6111,30 +6116,137 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Börje H Fagerlind</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373722</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>64923333</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden söder om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>446590</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6585573</v>
+      </c>
+      <c r="S51" t="n">
+        <v>50</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Kristinehams Naturskyddsförening utflykt 9/4-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/64923333</t>
         </is>
@@ -6191,6 +6303,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -6028,7 +6028,7 @@
         <v>137373722</v>
       </c>
       <c r="B50" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
